--- a/output_plant/stomata_Intermediate_kuerschner_2008.xlsx
+++ b/output_plant/stomata_Intermediate_kuerschner_2008.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
   <si>
     <t>eDab</t>
   </si>
@@ -609,7 +609,7 @@
     <t xml:space="preserve">10.1073/pnas.0708588105</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-si_kuerschner_2008.xlsx</t>
+    <t xml:space="preserve">stomata-si_kuerschner_2008_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -690,7 +690,7 @@
     <t xml:space="preserve">1993/28/32/2,1993/28/34A/1,1993/29/26B/3,KR76,Pic</t>
   </si>
   <si>
-    <t xml:space="preserve">Data: species specific mean CO2 estimates from Kurschner et al 2008 as published in Figure 3b; Data: species specific mean CO2 estimates from Kurschner et al 2008 as published in Figure 3b; actual pos. CO2 uncertainty is unbounded but has been set to 2000 ppm for plotting ourposes</t>
+    <t xml:space="preserve">Data: species specific mean CO2 estimates from Kurschner et al 2008 as published in Figure 3b; actual pos. CO2 uncertainty is unbounded but has been set to 2000 ppm for plotting ourposes</t>
   </si>
   <si>
     <t xml:space="preserve">KR508,KR181,Sch469/1,Sch673/1</t>
@@ -709,6 +709,9 @@
   </si>
   <si>
     <t xml:space="preserve">VJK237-12A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR390,MR322</t>
   </si>
 </sst>
 </file>
@@ -3647,11 +3650,95 @@
       </c>
     </row>
     <row r="23">
-      <c r="H23" s="23"/>
+      <c r="A23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C23" t="s">
+        <v>198</v>
+      </c>
+      <c r="D23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23" s="23" t="n">
+        <v>25.17</v>
+      </c>
       <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="BK23" s="1"/>
+      <c r="J23" s="23" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="K23" s="23" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L23" t="s">
+        <v>201</v>
+      </c>
+      <c r="M23" t="s">
+        <v>215</v>
+      </c>
+      <c r="N23" t="s">
+        <v>203</v>
+      </c>
+      <c r="O23" t="s">
+        <v>216</v>
+      </c>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23"/>
+      <c r="AF23"/>
+      <c r="AG23"/>
+      <c r="AH23"/>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23"/>
+      <c r="AL23"/>
+      <c r="AM23"/>
+      <c r="AN23"/>
+      <c r="AO23"/>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23"/>
+      <c r="AS23"/>
+      <c r="AT23"/>
+      <c r="AU23"/>
+      <c r="AV23"/>
+      <c r="AW23"/>
+      <c r="AX23"/>
+      <c r="AY23"/>
+      <c r="AZ23"/>
+      <c r="BA23"/>
+      <c r="BB23"/>
+      <c r="BC23"/>
+      <c r="BD23"/>
+      <c r="BE23"/>
+      <c r="BF23"/>
+      <c r="BG23"/>
+      <c r="BH23"/>
+      <c r="BI23"/>
+      <c r="BJ23"/>
+      <c r="BK23" s="1" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="24">
       <c r="H24" s="23"/>

--- a/output_plant/stomata_Intermediate_kuerschner_2008.xlsx
+++ b/output_plant/stomata_Intermediate_kuerschner_2008.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
   <si>
     <t>eDab</t>
   </si>
@@ -618,7 +618,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Absolute age of the biozone, palaeomagnetic Chron, or geological stage depending upon the age assessment available</t>
+    <t xml:space="preserve">Absolute age of the biozone, palaeomagnetic Chron, or geological stage depending upon the age assessment available; Biostratigraphy updated to GTS2020</t>
   </si>
   <si>
     <t xml:space="preserve">Lauraceae / Laurus</t>
@@ -636,6 +636,9 @@
     <t xml:space="preserve">GA</t>
   </si>
   <si>
+    <t xml:space="preserve">Absolute age of the biozone, palaeomagnetic Chron, or geological stage depending upon the age assessment available; Biostratigraphy updated to GTS2020; Absolute age of the biozone, palaeomagnetic Chron, or geological stage depending upon the age assessment available; L. Badenian (Schaefer A, Utescher T, Moers T (2004) Newslett Stratigr 40:73-110); Biostratigraphy updated to GTS2020</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ginkgoaceae / Ginkgo</t>
   </si>
   <si>
@@ -654,6 +657,9 @@
     <t xml:space="preserve">HB2/1,HB2/2</t>
   </si>
   <si>
+    <t xml:space="preserve">Absolute age of the biozone, palaeomagnetic Chron, or geological stage depending upon the age assessment available; Biostratigraphy updated to GTS2020; Absolute age of the biozone, palaeomagnetic Chron, or geological stage depending upon the age assessment available; E. Badenian (Němejc F, Kvaček Z, Pacltová B, Konzalová M (2003) Acta Univ Carol Geol 46:121-176); Biostratigraphy updated to GTS2020</t>
+  </si>
+  <si>
     <t xml:space="preserve">MY18,Taken from Literature (5)</t>
   </si>
   <si>
@@ -676,6 +682,9 @@
   </si>
   <si>
     <t xml:space="preserve">Literature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute age of the biozone, palaeomagnetic Chron, or geological stage depending upon the age assessment available; Biostratigraphy updated to GTS2020; Absolute age of the biozone, palaeomagnetic Chron, or geological stage depending upon the age assessment available; E. Badenian (Retallack GJ (2002) Philos Trans R Soc London A 360:959-673); Biostratigraphy updated to GTS2020</t>
   </si>
   <si>
     <t xml:space="preserve">HV1-25,HV1_28-1,HV11-31</t>
@@ -2131,16 +2140,16 @@
         <v>14</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P6" s="26"/>
       <c r="Q6" s="26"/>
@@ -2190,12 +2199,12 @@
       <c r="BI6" s="1"/>
       <c r="BJ6" s="1"/>
       <c r="BK6" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>197</v>
@@ -2286,7 +2295,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>197</v>
@@ -2313,16 +2322,16 @@
         <v>15.97</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P8" s="26"/>
       <c r="Q8" s="26"/>
@@ -2372,12 +2381,12 @@
       <c r="BI8" s="1"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>197</v>
@@ -2468,7 +2477,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>197</v>
@@ -2498,13 +2507,13 @@
         <v>201</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P10" s="26"/>
       <c r="Q10" s="26"/>
@@ -2559,7 +2568,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>197</v>
@@ -2589,13 +2598,13 @@
         <v>201</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P11" s="26"/>
       <c r="Q11" s="26"/>
@@ -2650,7 +2659,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>197</v>
@@ -2677,16 +2686,16 @@
         <v>15.97</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P12" s="26"/>
       <c r="Q12" s="26"/>
@@ -2736,12 +2745,12 @@
       <c r="BI12" s="1"/>
       <c r="BJ12" s="1"/>
       <c r="BK12" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>197</v>
@@ -2832,7 +2841,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>197</v>
@@ -2862,13 +2871,13 @@
         <v>201</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P14" s="26"/>
       <c r="Q14" s="26"/>
@@ -2923,7 +2932,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B15" t="s">
         <v>197</v>
@@ -2953,13 +2962,13 @@
         <v>201</v>
       </c>
       <c r="M15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N15" t="s">
         <v>203</v>
       </c>
       <c r="O15" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P15"/>
       <c r="Q15"/>
@@ -3014,7 +3023,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B16" t="s">
         <v>197</v>
@@ -3100,12 +3109,12 @@
       <c r="BI16"/>
       <c r="BJ16"/>
       <c r="BK16" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B17" t="s">
         <v>197</v>
@@ -3135,13 +3144,13 @@
         <v>201</v>
       </c>
       <c r="M17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N17" t="s">
         <v>203</v>
       </c>
       <c r="O17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P17"/>
       <c r="Q17"/>
@@ -3196,7 +3205,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s">
         <v>197</v>
@@ -3226,13 +3235,13 @@
         <v>201</v>
       </c>
       <c r="M18" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N18" t="s">
         <v>203</v>
       </c>
       <c r="O18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
@@ -3287,7 +3296,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s">
         <v>197</v>
@@ -3378,7 +3387,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s">
         <v>197</v>
@@ -3408,13 +3417,13 @@
         <v>201</v>
       </c>
       <c r="M20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N20" t="s">
         <v>203</v>
       </c>
       <c r="O20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P20"/>
       <c r="Q20"/>
@@ -3469,7 +3478,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
         <v>197</v>
@@ -3499,13 +3508,13 @@
         <v>201</v>
       </c>
       <c r="M21" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s">
         <v>203</v>
       </c>
       <c r="O21" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
@@ -3560,7 +3569,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s">
         <v>197</v>
@@ -3590,13 +3599,13 @@
         <v>201</v>
       </c>
       <c r="M22" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s">
         <v>203</v>
       </c>
       <c r="O22" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P22"/>
       <c r="Q22"/>
@@ -3651,7 +3660,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s">
         <v>197</v>
@@ -3681,13 +3690,13 @@
         <v>201</v>
       </c>
       <c r="M23" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s">
         <v>203</v>
       </c>
       <c r="O23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P23"/>
       <c r="Q23"/>
